--- a/physician_forms/004_hospital_satisfaction_survey--physician_forms.xlsx
+++ b/physician_forms/004_hospital_satisfaction_survey--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1158,8 +1158,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_15_minutes'}</t>
+          <t>less_than_15_minutes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 15 minutes'}</t>
+          <t>Less than 15 minutes</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'15-30_minutes'}</t>
+          <t>15-30_minutes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '15-30 minutes'}</t>
+          <t>15-30 minutes</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'30-45_minutes'}</t>
+          <t>30-45_minutes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '30-45 minutes'}</t>
+          <t>30-45 minutes</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_60_minutes'}</t>
+          <t>more_than_60_minutes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'More than 60 minutes'}</t>
+          <t>More than 60 minutes</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very low'}</t>
+          <t>Very low</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very high'}</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Very low'}</t>
+          <t>Very low</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Very high'}</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Not likely'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unlikely'}</t>
+          <t>somewhat_unlikely</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat unlikely'}</t>
+          <t>Somewhat unlikely</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
